--- a/feedback_surveys/023_grinder_pump_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/023_grinder_pump_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>underground</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Underground</t>
+          <t>Inside</t>
         </is>
       </c>
     </row>
@@ -1611,80 +1611,80 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inside</t>
+          <t>Outside</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pump_location_type_choices</t>
+          <t>pump_location_visibility_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>outside</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Outside</t>
+          <t>Inside</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pump_location_type_choices</t>
+          <t>pump_location_visibility_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inside</t>
+          <t>Outside</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pump_location_visibility_choices</t>
+          <t>pump_location_size_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inside</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pump_location_visibility_choices</t>
+          <t>pump_location_size_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>outside</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Outside</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1696,46 +1696,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pump_location_size_choices</t>
+          <t>pump_location_depth_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>less_than_20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Less Than 20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pump_location_size_choices</t>
+          <t>pump_location_depth_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>20-40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>20-40</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>less_than_20</t>
+          <t>40-60</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Less Than 20</t>
+          <t>40-60</t>
         </is>
       </c>
     </row>
@@ -1764,46 +1764,46 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20-40</t>
+          <t>more_than_60</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20-40</t>
+          <t>More Than 60</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pump_location_depth_choices</t>
+          <t>pump_location_elevation_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>40-60</t>
+          <t>lowest_point</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>40-60</t>
+          <t>Lowest Point</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pump_location_depth_choices</t>
+          <t>pump_location_elevation_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>more_than_60</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>More Than 60</t>
+          <t>Middle</t>
         </is>
       </c>
     </row>
@@ -1815,44 +1815,10 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>lowest_point</t>
+          <t>highest_point</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
-        <is>
-          <t>Lowest Point</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>pump_location_elevation_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Middle</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>pump_location_elevation_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>highest_point</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
         <is>
           <t>Highest Point</t>
         </is>
